--- a/labeled/Add_Eating/July/classification_results.xlsx
+++ b/labeled/Add_Eating/July/classification_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,14 +524,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -596,37 +596,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -668,19 +668,19 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -830,73 +830,73 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -938,19 +938,19 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -974,19 +974,19 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1046,19 +1046,19 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1118,19 +1118,19 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1226,19 +1226,19 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1262,19 +1262,19 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1406,19 +1406,19 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1442,32 +1442,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B58" t="n">
         <v>0</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1496,37 +1496,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1550,19 +1550,19 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1604,37 +1604,37 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1676,19 +1676,19 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1766,73 +1766,73 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1856,19 +1856,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1964,19 +1964,19 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2018,19 +2018,19 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2072,19 +2072,19 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2108,19 +2108,19 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2162,19 +2162,19 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2216,37 +2216,37 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2288,50 +2288,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2342,55 +2342,55 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2432,19 +2432,19 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2558,50 +2558,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B121" t="n">
         <v>0</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2666,37 +2666,37 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2774,14 +2774,14 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B131" t="n">
         <v>0</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -2792,73 +2792,73 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2900,19 +2900,19 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2936,37 +2936,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2990,37 +2990,37 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3062,37 +3062,37 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3152,55 +3152,55 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="B156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3278,68 +3278,68 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B162" t="n">
         <v>1</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3350,73 +3350,73 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3440,86 +3440,86 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B172" t="n">
         <v>0</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3530,19 +3530,19 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3566,109 +3566,109 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B175" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3692,73 +3692,73 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3782,37 +3782,37 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3836,37 +3836,37 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3890,19 +3890,19 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>1</v>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3920,43 +3920,43 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3980,19 +3980,19 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4016,19 +4016,19 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4070,55 +4070,55 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4142,73 +4142,73 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4250,37 +4250,37 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4304,19 +4304,19 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4340,91 +4340,91 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4448,14 +4448,14 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B224" t="n">
         <v>1</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -4466,19 +4466,19 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4502,19 +4502,19 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4538,50 +4538,50 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B231" t="n">
         <v>1</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -4592,19 +4592,19 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -4646,19 +4646,19 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4718,14 +4718,14 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B239" t="n">
         <v>2</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -4736,19 +4736,19 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4785,6 +4785,3408 @@
       <c r="D242" t="inlineStr">
         <is>
           <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>1</v>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>1</v>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>1</v>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>1</v>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>1</v>
+      </c>
+      <c r="B247" t="n">
+        <v>2</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>1</v>
+      </c>
+      <c r="B248" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>1</v>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1</v>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>1</v>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>1</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>1</v>
+      </c>
+      <c r="B253" t="n">
+        <v>0</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>1</v>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>1</v>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>1</v>
+      </c>
+      <c r="B256" t="n">
+        <v>1</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>1</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>1</v>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>1</v>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>1</v>
+      </c>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>1</v>
+      </c>
+      <c r="B261" t="n">
+        <v>2</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>1</v>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>1</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>1</v>
+      </c>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>1</v>
+      </c>
+      <c r="B265" t="n">
+        <v>1</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>1</v>
+      </c>
+      <c r="B266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>1</v>
+      </c>
+      <c r="B267" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>1</v>
+      </c>
+      <c r="B268" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>1</v>
+      </c>
+      <c r="B269" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>1</v>
+      </c>
+      <c r="B270" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>1</v>
+      </c>
+      <c r="B271" t="n">
+        <v>0</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>1</v>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>1</v>
+      </c>
+      <c r="B273" t="n">
+        <v>1</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>1</v>
+      </c>
+      <c r="B274" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>1</v>
+      </c>
+      <c r="B275" t="n">
+        <v>1</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>1</v>
+      </c>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>1</v>
+      </c>
+      <c r="B277" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>1</v>
+      </c>
+      <c r="B278" t="n">
+        <v>1</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>1</v>
+      </c>
+      <c r="B279" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2</v>
+      </c>
+      <c r="B280" t="n">
+        <v>2</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2</v>
+      </c>
+      <c r="B281" t="n">
+        <v>2</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2</v>
+      </c>
+      <c r="B282" t="n">
+        <v>2</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>2</v>
+      </c>
+      <c r="B283" t="n">
+        <v>2</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2</v>
+      </c>
+      <c r="B284" t="n">
+        <v>2</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>2</v>
+      </c>
+      <c r="B285" t="n">
+        <v>2</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>2</v>
+      </c>
+      <c r="B286" t="n">
+        <v>2</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>2</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2</v>
+      </c>
+      <c r="B288" t="n">
+        <v>2</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>2</v>
+      </c>
+      <c r="B289" t="n">
+        <v>2</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>2</v>
+      </c>
+      <c r="B290" t="n">
+        <v>2</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2</v>
+      </c>
+      <c r="B291" t="n">
+        <v>2</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2</v>
+      </c>
+      <c r="B292" t="n">
+        <v>2</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2</v>
+      </c>
+      <c r="B293" t="n">
+        <v>2</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2</v>
+      </c>
+      <c r="B294" t="n">
+        <v>2</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2</v>
+      </c>
+      <c r="B295" t="n">
+        <v>2</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2</v>
+      </c>
+      <c r="B296" t="n">
+        <v>2</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2</v>
+      </c>
+      <c r="B297" t="n">
+        <v>2</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2</v>
+      </c>
+      <c r="B298" t="n">
+        <v>2</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2</v>
+      </c>
+      <c r="B299" t="n">
+        <v>1</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>2</v>
+      </c>
+      <c r="B300" t="n">
+        <v>2</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>2</v>
+      </c>
+      <c r="B301" t="n">
+        <v>2</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>2</v>
+      </c>
+      <c r="B302" t="n">
+        <v>2</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>2</v>
+      </c>
+      <c r="B303" t="n">
+        <v>2</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>2</v>
+      </c>
+      <c r="B304" t="n">
+        <v>2</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>2</v>
+      </c>
+      <c r="B305" t="n">
+        <v>2</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>2</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>2</v>
+      </c>
+      <c r="B307" t="n">
+        <v>2</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>2</v>
+      </c>
+      <c r="B308" t="n">
+        <v>2</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>2</v>
+      </c>
+      <c r="B309" t="n">
+        <v>2</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>2</v>
+      </c>
+      <c r="B310" t="n">
+        <v>2</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>2</v>
+      </c>
+      <c r="B311" t="n">
+        <v>2</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>2</v>
+      </c>
+      <c r="B312" t="n">
+        <v>2</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>2</v>
+      </c>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>2</v>
+      </c>
+      <c r="B314" t="n">
+        <v>2</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>2</v>
+      </c>
+      <c r="B315" t="n">
+        <v>2</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>2</v>
+      </c>
+      <c r="B316" t="n">
+        <v>2</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>2</v>
+      </c>
+      <c r="B317" t="n">
+        <v>0</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>2</v>
+      </c>
+      <c r="B318" t="n">
+        <v>1</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>2</v>
+      </c>
+      <c r="B319" t="n">
+        <v>2</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>2</v>
+      </c>
+      <c r="B320" t="n">
+        <v>2</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>2</v>
+      </c>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>2</v>
+      </c>
+      <c r="B322" t="n">
+        <v>2</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>2</v>
+      </c>
+      <c r="B323" t="n">
+        <v>0</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>2</v>
+      </c>
+      <c r="B324" t="n">
+        <v>0</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>2</v>
+      </c>
+      <c r="B325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>2</v>
+      </c>
+      <c r="B326" t="n">
+        <v>2</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>2</v>
+      </c>
+      <c r="B327" t="n">
+        <v>2</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>2</v>
+      </c>
+      <c r="B328" t="n">
+        <v>2</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>2</v>
+      </c>
+      <c r="B329" t="n">
+        <v>0</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>2</v>
+      </c>
+      <c r="B330" t="n">
+        <v>2</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>2</v>
+      </c>
+      <c r="B331" t="n">
+        <v>2</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>2</v>
+      </c>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>2</v>
+      </c>
+      <c r="B333" t="n">
+        <v>2</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>2</v>
+      </c>
+      <c r="B334" t="n">
+        <v>1</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>2</v>
+      </c>
+      <c r="B335" t="n">
+        <v>2</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>2</v>
+      </c>
+      <c r="B336" t="n">
+        <v>2</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>2</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>2</v>
+      </c>
+      <c r="B338" t="n">
+        <v>1</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>2</v>
+      </c>
+      <c r="B339" t="n">
+        <v>2</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>2</v>
+      </c>
+      <c r="B340" t="n">
+        <v>2</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>2</v>
+      </c>
+      <c r="B341" t="n">
+        <v>2</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>2</v>
+      </c>
+      <c r="B342" t="n">
+        <v>2</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>2</v>
+      </c>
+      <c r="B343" t="n">
+        <v>2</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>2</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>2</v>
+      </c>
+      <c r="B345" t="n">
+        <v>2</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>2</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>2</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>2</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>2</v>
+      </c>
+      <c r="B349" t="n">
+        <v>2</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>2</v>
+      </c>
+      <c r="B350" t="n">
+        <v>2</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>2</v>
+      </c>
+      <c r="B351" t="n">
+        <v>2</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>2</v>
+      </c>
+      <c r="B352" t="n">
+        <v>2</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>2</v>
+      </c>
+      <c r="B353" t="n">
+        <v>2</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>2</v>
+      </c>
+      <c r="B354" t="n">
+        <v>2</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>2</v>
+      </c>
+      <c r="B355" t="n">
+        <v>2</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>2</v>
+      </c>
+      <c r="B356" t="n">
+        <v>2</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>2</v>
+      </c>
+      <c r="B357" t="n">
+        <v>2</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>2</v>
+      </c>
+      <c r="B358" t="n">
+        <v>2</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>2</v>
+      </c>
+      <c r="B359" t="n">
+        <v>0</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>2</v>
+      </c>
+      <c r="B360" t="n">
+        <v>2</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>2</v>
+      </c>
+      <c r="B361" t="n">
+        <v>2</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>2</v>
+      </c>
+      <c r="B362" t="n">
+        <v>0</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>2</v>
+      </c>
+      <c r="B363" t="n">
+        <v>2</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>2</v>
+      </c>
+      <c r="B364" t="n">
+        <v>2</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>2</v>
+      </c>
+      <c r="B365" t="n">
+        <v>2</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>2</v>
+      </c>
+      <c r="B366" t="n">
+        <v>2</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>2</v>
+      </c>
+      <c r="B367" t="n">
+        <v>2</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>2</v>
+      </c>
+      <c r="B368" t="n">
+        <v>2</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>2</v>
+      </c>
+      <c r="B369" t="n">
+        <v>2</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>2</v>
+      </c>
+      <c r="B370" t="n">
+        <v>2</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>2</v>
+      </c>
+      <c r="B371" t="n">
+        <v>2</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>2</v>
+      </c>
+      <c r="B372" t="n">
+        <v>2</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>2</v>
+      </c>
+      <c r="B373" t="n">
+        <v>2</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>2</v>
+      </c>
+      <c r="B374" t="n">
+        <v>2</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>2</v>
+      </c>
+      <c r="B375" t="n">
+        <v>2</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>2</v>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>2</v>
+      </c>
+      <c r="B377" t="n">
+        <v>2</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>2</v>
+      </c>
+      <c r="B378" t="n">
+        <v>2</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>2</v>
+      </c>
+      <c r="B379" t="n">
+        <v>1</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>2</v>
+      </c>
+      <c r="B380" t="n">
+        <v>2</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>2</v>
+      </c>
+      <c r="B381" t="n">
+        <v>2</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>2</v>
+      </c>
+      <c r="B382" t="n">
+        <v>2</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>2</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>2</v>
+      </c>
+      <c r="B384" t="n">
+        <v>2</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>2</v>
+      </c>
+      <c r="B385" t="n">
+        <v>2</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>2</v>
+      </c>
+      <c r="B386" t="n">
+        <v>2</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>2</v>
+      </c>
+      <c r="B387" t="n">
+        <v>2</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>2</v>
+      </c>
+      <c r="B388" t="n">
+        <v>2</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>2</v>
+      </c>
+      <c r="B389" t="n">
+        <v>2</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>2</v>
+      </c>
+      <c r="B390" t="n">
+        <v>2</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>2</v>
+      </c>
+      <c r="B391" t="n">
+        <v>2</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>2</v>
+      </c>
+      <c r="B392" t="n">
+        <v>2</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>2</v>
+      </c>
+      <c r="B393" t="n">
+        <v>2</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>2</v>
+      </c>
+      <c r="B394" t="n">
+        <v>2</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>2</v>
+      </c>
+      <c r="B395" t="n">
+        <v>1</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>2</v>
+      </c>
+      <c r="B396" t="n">
+        <v>2</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>2</v>
+      </c>
+      <c r="B397" t="n">
+        <v>0</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>2</v>
+      </c>
+      <c r="B398" t="n">
+        <v>2</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>2</v>
+      </c>
+      <c r="B399" t="n">
+        <v>2</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>2</v>
+      </c>
+      <c r="B400" t="n">
+        <v>2</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>2</v>
+      </c>
+      <c r="B401" t="n">
+        <v>2</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>2</v>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>2</v>
+      </c>
+      <c r="B403" t="n">
+        <v>2</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>2</v>
+      </c>
+      <c r="B404" t="n">
+        <v>2</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>2</v>
+      </c>
+      <c r="B405" t="n">
+        <v>1</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>2</v>
+      </c>
+      <c r="B406" t="n">
+        <v>2</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>2</v>
+      </c>
+      <c r="B407" t="n">
+        <v>2</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>2</v>
+      </c>
+      <c r="B408" t="n">
+        <v>2</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>2</v>
+      </c>
+      <c r="B409" t="n">
+        <v>2</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>2</v>
+      </c>
+      <c r="B410" t="n">
+        <v>2</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>2</v>
+      </c>
+      <c r="B411" t="n">
+        <v>2</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>2</v>
+      </c>
+      <c r="B412" t="n">
+        <v>1</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>2</v>
+      </c>
+      <c r="B413" t="n">
+        <v>2</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>2</v>
+      </c>
+      <c r="B414" t="n">
+        <v>2</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>2</v>
+      </c>
+      <c r="B415" t="n">
+        <v>2</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>2</v>
+      </c>
+      <c r="B416" t="n">
+        <v>2</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>2</v>
+      </c>
+      <c r="B417" t="n">
+        <v>1</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>2</v>
+      </c>
+      <c r="B418" t="n">
+        <v>2</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>2</v>
+      </c>
+      <c r="B419" t="n">
+        <v>2</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>2</v>
+      </c>
+      <c r="B420" t="n">
+        <v>2</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>2</v>
+      </c>
+      <c r="B421" t="n">
+        <v>2</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>2</v>
+      </c>
+      <c r="B422" t="n">
+        <v>2</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>2</v>
+      </c>
+      <c r="B423" t="n">
+        <v>2</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>2</v>
+      </c>
+      <c r="B424" t="n">
+        <v>0</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Not_Drinking</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>2</v>
+      </c>
+      <c r="B425" t="n">
+        <v>2</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>2</v>
+      </c>
+      <c r="B426" t="n">
+        <v>2</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>2</v>
+      </c>
+      <c r="B427" t="n">
+        <v>2</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>2</v>
+      </c>
+      <c r="B428" t="n">
+        <v>2</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>2</v>
+      </c>
+      <c r="B429" t="n">
+        <v>2</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>2</v>
+      </c>
+      <c r="B430" t="n">
+        <v>2</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>2</v>
+      </c>
+      <c r="B431" t="n">
+        <v>2</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Eating</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Eating</t>
         </is>
       </c>
     </row>

--- a/labeled/Add_Eating/July/classification_results.xlsx
+++ b/labeled/Add_Eating/July/classification_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D431"/>
+  <dimension ref="A1:D430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -2738,19 +2738,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="B232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
         <v>1</v>
       </c>
       <c r="B239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
         <v>1</v>
       </c>
       <c r="B241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="B247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
         <v>1</v>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="B261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
         <v>1</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -5438,14 +5438,14 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B279" t="n">
         <v>1</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -5693,7 +5693,7 @@
         <v>2</v>
       </c>
       <c r="B293" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
         <v>2</v>
       </c>
       <c r="B305" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
         <v>2</v>
       </c>
       <c r="B312" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
         <v>2</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
         <v>2</v>
       </c>
       <c r="B314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
         <v>2</v>
       </c>
       <c r="B316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
         <v>2</v>
       </c>
       <c r="B318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>2</v>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
         <v>2</v>
       </c>
       <c r="B323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
         <v>2</v>
       </c>
       <c r="B324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
         <v>2</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
         <v>2</v>
       </c>
       <c r="B331" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         <v>2</v>
       </c>
       <c r="B332" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
         <v>2</v>
       </c>
       <c r="B334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
         <v>2</v>
       </c>
       <c r="B350" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
         <v>2</v>
       </c>
       <c r="B359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
         <v>2</v>
       </c>
       <c r="B362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
         <v>2</v>
       </c>
       <c r="B366" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
         <v>2</v>
       </c>
       <c r="B368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
         <v>2</v>
       </c>
       <c r="B376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
         <v>2</v>
       </c>
       <c r="B386" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
         <v>2</v>
       </c>
       <c r="B395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
         <v>2</v>
       </c>
       <c r="B397" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
         <v>2</v>
       </c>
       <c r="B399" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
         <v>2</v>
       </c>
       <c r="B402" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
         <v>2</v>
       </c>
       <c r="B405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
         <v>2</v>
       </c>
       <c r="B409" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7799,7 @@
         <v>2</v>
       </c>
       <c r="B410" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
         <v>2</v>
       </c>
       <c r="B412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
         <v>2</v>
       </c>
       <c r="B413" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
         <v>2</v>
       </c>
       <c r="B417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -8051,7 +8051,7 @@
         <v>2</v>
       </c>
       <c r="B424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -8167,24 +8167,6 @@
         </is>
       </c>
       <c r="D430" t="inlineStr">
-        <is>
-          <t>Eating</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="n">
-        <v>2</v>
-      </c>
-      <c r="B431" t="n">
-        <v>2</v>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>Eating</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
         <is>
           <t>Eating</t>
         </is>

--- a/labeled/Add_Eating/July/classification_results.xlsx
+++ b/labeled/Add_Eating/July/classification_results.xlsx
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="B154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="B155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="B182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -4253,7 +4253,7 @@
         <v>1</v>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -4271,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         <v>1</v>
       </c>
       <c r="B268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5477,7 @@
         <v>2</v>
       </c>
       <c r="B281" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
         <v>2</v>
       </c>
       <c r="B291" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
         <v>2</v>
       </c>
       <c r="B292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
         <v>2</v>
       </c>
       <c r="B311" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
         <v>2</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
         <v>2</v>
       </c>
       <c r="B324" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
         <v>2</v>
       </c>
       <c r="B325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6449,7 @@
         <v>2</v>
       </c>
       <c r="B335" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6593,7 @@
         <v>2</v>
       </c>
       <c r="B343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
         <v>2</v>
       </c>
       <c r="B350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
         <v>2</v>
       </c>
       <c r="B351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
         <v>2</v>
       </c>
       <c r="B356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
         <v>2</v>
       </c>
       <c r="B409" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
         <v>2</v>
       </c>
       <c r="B413" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Not_Drinking</t>
+          <t>Eating</t>
         </is>
       </c>
     </row>
@@ -8033,7 +8033,7 @@
         <v>2</v>
       </c>
       <c r="B423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8087,7 @@
         <v>2</v>
       </c>
       <c r="B426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Drinking</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
         <v>2</v>
       </c>
       <c r="B427" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Eating</t>
+          <t>Not_Drinking</t>
         </is>
       </c>
     </row>
